--- a/examples/output/MNL_modeChoice_SP_WTP.xlsx
+++ b/examples/output/MNL_modeChoice_SP_WTP.xlsx
@@ -898,7 +898,7 @@
         <v>27</v>
       </c>
       <c r="B6">
-        <v>2.069427013397217</v>
+        <v>2.3391242027282715</v>
       </c>
     </row>
     <row r="7" spans="1:2">

--- a/examples/output/MNL_modeChoice_SP_WTP.xlsx
+++ b/examples/output/MNL_modeChoice_SP_WTP.xlsx
@@ -898,7 +898,7 @@
         <v>27</v>
       </c>
       <c r="B6">
-        <v>2.3391242027282715</v>
+        <v>2.1373510360717773</v>
       </c>
     </row>
     <row r="7" spans="1:2">

--- a/examples/output/MNL_modeChoice_SP_WTP.xlsx
+++ b/examples/output/MNL_modeChoice_SP_WTP.xlsx
@@ -898,7 +898,7 @@
         <v>27</v>
       </c>
       <c r="B6">
-        <v>2.1373510360717773</v>
+        <v>2.033996105194092</v>
       </c>
     </row>
     <row r="7" spans="1:2">

--- a/examples/output/MNL_modeChoice_SP_WTP.xlsx
+++ b/examples/output/MNL_modeChoice_SP_WTP.xlsx
@@ -898,7 +898,7 @@
         <v>27</v>
       </c>
       <c r="B6">
-        <v>2.033996105194092</v>
+        <v>2.0615601539611816</v>
       </c>
     </row>
     <row r="7" spans="1:2">

--- a/examples/output/MNL_modeChoice_SP_WTP.xlsx
+++ b/examples/output/MNL_modeChoice_SP_WTP.xlsx
@@ -898,7 +898,7 @@
         <v>27</v>
       </c>
       <c r="B6">
-        <v>2.0615601539611816</v>
+        <v>1.7139079570770264</v>
       </c>
     </row>
     <row r="7" spans="1:2">

--- a/examples/output/MNL_modeChoice_SP_WTP.xlsx
+++ b/examples/output/MNL_modeChoice_SP_WTP.xlsx
@@ -898,7 +898,7 @@
         <v>27</v>
       </c>
       <c r="B6">
-        <v>1.7139079570770264</v>
+        <v>1.5899240970611572</v>
       </c>
     </row>
     <row r="7" spans="1:2">

--- a/examples/output/MNL_modeChoice_SP_WTP.xlsx
+++ b/examples/output/MNL_modeChoice_SP_WTP.xlsx
@@ -898,7 +898,7 @@
         <v>27</v>
       </c>
       <c r="B6">
-        <v>1.5899240970611572</v>
+        <v>1.491899013519287</v>
       </c>
     </row>
     <row r="7" spans="1:2">

--- a/examples/output/MNL_modeChoice_SP_WTP.xlsx
+++ b/examples/output/MNL_modeChoice_SP_WTP.xlsx
@@ -898,7 +898,7 @@
         <v>27</v>
       </c>
       <c r="B6">
-        <v>1.491899013519287</v>
+        <v>1.4912850856781006</v>
       </c>
     </row>
     <row r="7" spans="1:2">

--- a/examples/output/MNL_modeChoice_SP_WTP.xlsx
+++ b/examples/output/MNL_modeChoice_SP_WTP.xlsx
@@ -898,7 +898,7 @@
         <v>27</v>
       </c>
       <c r="B6">
-        <v>1.4912850856781006</v>
+        <v>1.4401450157165527</v>
       </c>
     </row>
     <row r="7" spans="1:2">

--- a/examples/output/MNL_modeChoice_SP_WTP.xlsx
+++ b/examples/output/MNL_modeChoice_SP_WTP.xlsx
@@ -898,7 +898,7 @@
         <v>27</v>
       </c>
       <c r="B6">
-        <v>1.4401450157165527</v>
+        <v>1.4548768997192383</v>
       </c>
     </row>
     <row r="7" spans="1:2">

--- a/examples/output/MNL_modeChoice_SP_WTP.xlsx
+++ b/examples/output/MNL_modeChoice_SP_WTP.xlsx
@@ -510,25 +510,25 @@
         <v>8</v>
       </c>
       <c r="B2">
-        <v>0.23827657882964776</v>
+        <v>0.23827657882965722</v>
       </c>
       <c r="C2">
-        <v>0.34012439440973263</v>
+        <v>0.3401243944097453</v>
       </c>
       <c r="D2">
-        <v>0.7005571571635247</v>
+        <v>0.7005571571635265</v>
       </c>
       <c r="E2">
-        <v>0.48357942327549797</v>
+        <v>0.48357942327549663</v>
       </c>
       <c r="F2">
-        <v>0.34130176429487563</v>
+        <v>0.34130176429490133</v>
       </c>
       <c r="G2">
-        <v>0.6981404837502778</v>
+        <v>0.698140483750253</v>
       </c>
       <c r="H2">
-        <v>0.4850893424288585</v>
+        <v>0.485089342428874</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -536,25 +536,25 @@
         <v>9</v>
       </c>
       <c r="B3">
-        <v>0.06241069113659165</v>
+        <v>0.06241069113659562</v>
       </c>
       <c r="C3">
-        <v>0.5385498512551452</v>
+        <v>0.5385498512551189</v>
       </c>
       <c r="D3">
-        <v>0.11588656275948678</v>
+        <v>0.11588656275949981</v>
       </c>
       <c r="E3">
-        <v>0.9077424453041181</v>
+        <v>0.9077424453041076</v>
       </c>
       <c r="F3">
-        <v>0.5419638756835994</v>
+        <v>0.5419638756835291</v>
       </c>
       <c r="G3">
-        <v>0.11515655182344156</v>
+        <v>0.11515655182346382</v>
       </c>
       <c r="H3">
-        <v>0.9083210361233822</v>
+        <v>0.9083210361233645</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -588,22 +588,22 @@
         <v>11</v>
       </c>
       <c r="B5">
-        <v>-1.4813697360554865</v>
+        <v>-1.4813697360554827</v>
       </c>
       <c r="C5">
-        <v>0.3273248349026993</v>
+        <v>0.3273248349027114</v>
       </c>
       <c r="D5">
-        <v>-4.525686957104367</v>
+        <v>-4.525686957104188</v>
       </c>
       <c r="E5">
         <v>6.019963506131987e-6</v>
       </c>
       <c r="F5">
-        <v>0.32758816676811964</v>
+        <v>0.3275881667681455</v>
       </c>
       <c r="G5">
-        <v>-4.522048982019735</v>
+        <v>-4.522048982019366</v>
       </c>
       <c r="H5">
         <v>6.1243882301109664e-6</v>
@@ -614,22 +614,22 @@
         <v>12</v>
       </c>
       <c r="B6">
-        <v>0.3947290531957175</v>
+        <v>0.3947290531957182</v>
       </c>
       <c r="C6">
-        <v>0.045269922469758805</v>
+        <v>0.04526992246975915</v>
       </c>
       <c r="D6">
-        <v>8.719455030200333</v>
+        <v>8.719455030200281</v>
       </c>
       <c r="E6">
         <v>0.0</v>
       </c>
       <c r="F6">
-        <v>0.04498853658737999</v>
+        <v>0.04498853658738084</v>
       </c>
       <c r="G6">
-        <v>8.773991846323923</v>
+        <v>8.773991846323772</v>
       </c>
       <c r="H6">
         <v>0.0</v>
@@ -640,22 +640,22 @@
         <v>13</v>
       </c>
       <c r="B7">
-        <v>-6.970524736034377</v>
+        <v>-6.9705247360343705</v>
       </c>
       <c r="C7">
-        <v>0.8816680890567272</v>
+        <v>0.8816680890567276</v>
       </c>
       <c r="D7">
-        <v>-7.906064450503083</v>
+        <v>-7.906064450503072</v>
       </c>
       <c r="E7">
         <v>2.6645352591003757e-15</v>
       </c>
       <c r="F7">
-        <v>0.852371730041285</v>
+        <v>0.8523717300412857</v>
       </c>
       <c r="G7">
-        <v>-8.177799063909307</v>
+        <v>-8.177799063909292</v>
       </c>
       <c r="H7">
         <v>2.220446049250313e-16</v>
@@ -692,22 +692,22 @@
         <v>15</v>
       </c>
       <c r="B9">
-        <v>0.3315983080079117</v>
+        <v>0.33159830800791207</v>
       </c>
       <c r="C9">
-        <v>0.0428513676299767</v>
+        <v>0.042851367629977176</v>
       </c>
       <c r="D9">
-        <v>7.7383366353969505</v>
+        <v>7.738336635396873</v>
       </c>
       <c r="E9">
         <v>9.992007221626409e-15</v>
       </c>
       <c r="F9">
-        <v>0.043776715236937054</v>
+        <v>0.043776715236938116</v>
       </c>
       <c r="G9">
-        <v>7.574764488682381</v>
+        <v>7.574764488682206</v>
       </c>
       <c r="H9">
         <v>3.597122599785507e-14</v>
@@ -718,22 +718,22 @@
         <v>16</v>
       </c>
       <c r="B10">
-        <v>0.29560350633384613</v>
+        <v>0.29560350633384597</v>
       </c>
       <c r="C10">
-        <v>0.024964878641882474</v>
+        <v>0.024964878641881294</v>
       </c>
       <c r="D10">
-        <v>11.840774817063409</v>
+        <v>11.840774817063961</v>
       </c>
       <c r="E10">
         <v>0.0</v>
       </c>
       <c r="F10">
-        <v>0.025290371552796276</v>
+        <v>0.025290371552793407</v>
       </c>
       <c r="G10">
-        <v>11.688381316057106</v>
+        <v>11.688381316058425</v>
       </c>
       <c r="H10">
         <v>0.0</v>
@@ -744,22 +744,22 @@
         <v>17</v>
       </c>
       <c r="B11">
-        <v>0.19746403922656253</v>
+        <v>0.19746403922656225</v>
       </c>
       <c r="C11">
-        <v>0.010969884037327779</v>
+        <v>0.010969884037328174</v>
       </c>
       <c r="D11">
-        <v>18.000558488552993</v>
+        <v>18.00055848855232</v>
       </c>
       <c r="E11">
         <v>0.0</v>
       </c>
       <c r="F11">
-        <v>0.011307523382661892</v>
+        <v>0.011307523382662759</v>
       </c>
       <c r="G11">
-        <v>17.46306706995973</v>
+        <v>17.463067069958367</v>
       </c>
       <c r="H11">
         <v>0.0</v>
@@ -770,22 +770,22 @@
         <v>18</v>
       </c>
       <c r="B12">
-        <v>0.10832829631678006</v>
+        <v>0.10832829631677983</v>
       </c>
       <c r="C12">
-        <v>0.028564449171553555</v>
+        <v>0.02856444917155387</v>
       </c>
       <c r="D12">
-        <v>3.792416778849033</v>
+        <v>3.792416778848983</v>
       </c>
       <c r="E12">
         <v>0.00014918825414023118</v>
       </c>
       <c r="F12">
-        <v>0.02802065868965437</v>
+        <v>0.02802065868965549</v>
       </c>
       <c r="G12">
-        <v>3.866015339488662</v>
+        <v>3.866015339488499</v>
       </c>
       <c r="H12">
         <v>0.00011062798290506493</v>
@@ -796,22 +796,22 @@
         <v>19</v>
       </c>
       <c r="B13">
-        <v>-15.956777879543544</v>
+        <v>-15.95677787954353</v>
       </c>
       <c r="C13">
-        <v>0.8975449326685233</v>
+        <v>0.8975449326685244</v>
       </c>
       <c r="D13">
-        <v>-17.778249643838855</v>
+        <v>-17.77824964383882</v>
       </c>
       <c r="E13">
         <v>0.0</v>
       </c>
       <c r="F13">
-        <v>0.8920899258559507</v>
+        <v>0.8920899258559531</v>
       </c>
       <c r="G13">
-        <v>-17.88696118749821</v>
+        <v>-17.886961187498144</v>
       </c>
       <c r="H13">
         <v>0.0</v>
@@ -822,22 +822,22 @@
         <v>20</v>
       </c>
       <c r="B14">
-        <v>-0.058755939179563156</v>
+        <v>-0.05875593917956318</v>
       </c>
       <c r="C14">
-        <v>0.0014868312568994675</v>
+        <v>0.0014868312568994664</v>
       </c>
       <c r="D14">
-        <v>-39.517557158496</v>
+        <v>-39.51755715849604</v>
       </c>
       <c r="E14">
         <v>0.0</v>
       </c>
       <c r="F14">
-        <v>0.0014872228296132772</v>
+        <v>0.0014872228296132753</v>
       </c>
       <c r="G14">
-        <v>-39.50715253264467</v>
+        <v>-39.50715253264473</v>
       </c>
       <c r="H14">
         <v>0.0</v>
@@ -898,7 +898,7 @@
         <v>27</v>
       </c>
       <c r="B6">
-        <v>1.4548768997192383</v>
+        <v>1.5247669219970703</v>
       </c>
     </row>
     <row r="7" spans="1:2">

--- a/examples/output/MNL_modeChoice_SP_WTP.xlsx
+++ b/examples/output/MNL_modeChoice_SP_WTP.xlsx
@@ -898,7 +898,7 @@
         <v>27</v>
       </c>
       <c r="B6">
-        <v>1.5247669219970703</v>
+        <v>1.4154131412506104</v>
       </c>
     </row>
     <row r="7" spans="1:2">
